--- a/engine/techniques/bond_yield_forecast/resources/templates/bond_yield_forecast_input_template.xlsx
+++ b/engine/techniques/bond_yield_forecast/resources/templates/bond_yield_forecast_input_template.xlsx
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -863,6 +863,21 @@
           <t>Fed Funds Rate (quarterly average)</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Primary Budget Balance (% GDP)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unemployment Rate (%)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>6m Fed Funds Futures (market-implied %)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -879,6 +894,15 @@
       <c r="D2" t="n">
         <v>8.25</v>
       </c>
+      <c r="E2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.409000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -895,6 +919,15 @@
       <c r="D3" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="E3" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.163</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -911,6 +944,15 @@
       <c r="D4" t="n">
         <v>8.050000000000001</v>
       </c>
+      <c r="E4" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.065</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -927,6 +969,15 @@
       <c r="D5" t="n">
         <v>7.55</v>
       </c>
+      <c r="E5" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.465</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -943,6 +994,15 @@
       <c r="D6" t="n">
         <v>6.45</v>
       </c>
+      <c r="E6" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.287</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -959,6 +1019,15 @@
       <c r="D7" t="n">
         <v>5.85</v>
       </c>
+      <c r="E7" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.732</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -975,6 +1044,15 @@
       <c r="D8" t="n">
         <v>5.55</v>
       </c>
+      <c r="E8" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.471</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -991,6 +1069,15 @@
       <c r="D9" t="n">
         <v>4.85</v>
       </c>
+      <c r="E9" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.793</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1007,6 +1094,15 @@
       <c r="D10" t="n">
         <v>4.05</v>
       </c>
+      <c r="E10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.011</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1023,6 +1119,15 @@
       <c r="D11" t="n">
         <v>3.75</v>
       </c>
+      <c r="E11" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.819</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1039,6 +1144,15 @@
       <c r="D12" t="n">
         <v>3.25</v>
       </c>
+      <c r="E12" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.173</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1055,6 +1169,15 @@
       <c r="D13" t="n">
         <v>3.05</v>
       </c>
+      <c r="E13" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.894</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1071,6 +1194,15 @@
       <c r="D14" t="n">
         <v>3.05</v>
       </c>
+      <c r="E14" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1087,6 +1219,15 @@
       <c r="D15" t="n">
         <v>3</v>
       </c>
+      <c r="E15" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.214</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1103,6 +1244,15 @@
       <c r="D16" t="n">
         <v>3.05</v>
       </c>
+      <c r="E16" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.097</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1119,6 +1269,15 @@
       <c r="D17" t="n">
         <v>3</v>
       </c>
+      <c r="E17" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.979</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1135,6 +1294,15 @@
       <c r="D18" t="n">
         <v>3.3</v>
       </c>
+      <c r="E18" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.423</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1151,6 +1319,15 @@
       <c r="D19" t="n">
         <v>4</v>
       </c>
+      <c r="E19" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.099</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1167,6 +1344,15 @@
       <c r="D20" t="n">
         <v>4.5</v>
       </c>
+      <c r="E20" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1183,6 +1369,15 @@
       <c r="D21" t="n">
         <v>5.2</v>
       </c>
+      <c r="E21" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.371</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1199,6 +1394,15 @@
       <c r="D22" t="n">
         <v>5.95</v>
       </c>
+      <c r="E22" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.141</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1215,6 +1419,15 @@
       <c r="D23" t="n">
         <v>6</v>
       </c>
+      <c r="E23" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.386</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1231,6 +1444,15 @@
       <c r="D24" t="n">
         <v>5.75</v>
       </c>
+      <c r="E24" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.637</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1247,6 +1469,15 @@
       <c r="D25" t="n">
         <v>5.7</v>
       </c>
+      <c r="E25" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.694</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1263,6 +1494,15 @@
       <c r="D26" t="n">
         <v>5.3</v>
       </c>
+      <c r="E26" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.222</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1279,6 +1519,15 @@
       <c r="D27" t="n">
         <v>5.25</v>
       </c>
+      <c r="E27" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.482</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1295,6 +1544,15 @@
       <c r="D28" t="n">
         <v>5.3</v>
       </c>
+      <c r="E28" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5.155</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1311,6 +1569,15 @@
       <c r="D29" t="n">
         <v>5.3</v>
       </c>
+      <c r="E29" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.433</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1327,6 +1594,15 @@
       <c r="D30" t="n">
         <v>5.3</v>
       </c>
+      <c r="E30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.969</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1343,6 +1619,15 @@
       <c r="D31" t="n">
         <v>5.55</v>
       </c>
+      <c r="E31" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.927</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1359,6 +1644,15 @@
       <c r="D32" t="n">
         <v>5.55</v>
       </c>
+      <c r="E32" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.286</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1375,6 +1669,15 @@
       <c r="D33" t="n">
         <v>5.55</v>
       </c>
+      <c r="E33" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.522</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1391,6 +1694,15 @@
       <c r="D34" t="n">
         <v>5.5</v>
       </c>
+      <c r="E34" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.537</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1407,6 +1719,15 @@
       <c r="D35" t="n">
         <v>5.5</v>
       </c>
+      <c r="E35" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.533</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1423,6 +1744,15 @@
       <c r="D36" t="n">
         <v>5.55</v>
       </c>
+      <c r="E36" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5.536</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1439,6 +1769,15 @@
       <c r="D37" t="n">
         <v>4.85</v>
       </c>
+      <c r="E37" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.763</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1455,6 +1794,15 @@
       <c r="D38" t="n">
         <v>4.75</v>
       </c>
+      <c r="E38" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.65</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1471,6 +1819,15 @@
       <c r="D39" t="n">
         <v>4.75</v>
       </c>
+      <c r="E39" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.592</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1487,6 +1844,15 @@
       <c r="D40" t="n">
         <v>5.1</v>
       </c>
+      <c r="E40" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5.021</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1503,6 +1869,15 @@
       <c r="D41" t="n">
         <v>5.3</v>
       </c>
+      <c r="E41" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.352</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1519,6 +1894,15 @@
       <c r="D42" t="n">
         <v>5.65</v>
       </c>
+      <c r="E42" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.469</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1535,6 +1919,15 @@
       <c r="D43" t="n">
         <v>6.25</v>
       </c>
+      <c r="E43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.293</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1551,6 +1944,15 @@
       <c r="D44" t="n">
         <v>6.5</v>
       </c>
+      <c r="E44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.426</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1567,6 +1969,15 @@
       <c r="D45" t="n">
         <v>6.5</v>
       </c>
+      <c r="E45" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6.457</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1583,6 +1994,15 @@
       <c r="D46" t="n">
         <v>5.3</v>
       </c>
+      <c r="E46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5.067</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1599,6 +2019,15 @@
       <c r="D47" t="n">
         <v>4.3</v>
       </c>
+      <c r="E47" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.212</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1615,6 +2044,15 @@
       <c r="D48" t="n">
         <v>3.5</v>
       </c>
+      <c r="E48" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3.769</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1631,6 +2069,15 @@
       <c r="D49" t="n">
         <v>2.1</v>
       </c>
+      <c r="E49" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2.128</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1647,6 +2094,15 @@
       <c r="D50" t="n">
         <v>1.75</v>
       </c>
+      <c r="E50" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.792</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1663,6 +2119,15 @@
       <c r="D51" t="n">
         <v>1.75</v>
       </c>
+      <c r="E51" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.49</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1679,6 +2144,15 @@
       <c r="D52" t="n">
         <v>1.75</v>
       </c>
+      <c r="E52" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.709</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1695,6 +2169,15 @@
       <c r="D53" t="n">
         <v>1.45</v>
       </c>
+      <c r="E53" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.503</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1711,6 +2194,15 @@
       <c r="D54" t="n">
         <v>1.25</v>
       </c>
+      <c r="E54" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.178</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1727,6 +2219,15 @@
       <c r="D55" t="n">
         <v>1.25</v>
       </c>
+      <c r="E55" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.241</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1743,6 +2244,15 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.876</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1759,6 +2269,15 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
+      <c r="E57" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.134</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1775,6 +2294,15 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
+      <c r="E58" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.731</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1791,6 +2319,15 @@
       <c r="D59" t="n">
         <v>1.05</v>
       </c>
+      <c r="E59" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.082</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1807,6 +2344,15 @@
       <c r="D60" t="n">
         <v>1.55</v>
       </c>
+      <c r="E60" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.629</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1823,6 +2369,15 @@
       <c r="D61" t="n">
         <v>2</v>
       </c>
+      <c r="E61" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.92</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1839,6 +2394,15 @@
       <c r="D62" t="n">
         <v>2.55</v>
       </c>
+      <c r="E62" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2.61</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1855,6 +2419,15 @@
       <c r="D63" t="n">
         <v>3</v>
       </c>
+      <c r="E63" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.03</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1871,6 +2444,15 @@
       <c r="D64" t="n">
         <v>3.45</v>
       </c>
+      <c r="E64" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3.699</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1887,6 +2469,15 @@
       <c r="D65" t="n">
         <v>3.95</v>
       </c>
+      <c r="E65" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4.162</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1903,6 +2494,15 @@
       <c r="D66" t="n">
         <v>4.45</v>
       </c>
+      <c r="E66" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4.513</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1919,6 +2519,15 @@
       <c r="D67" t="n">
         <v>4.9</v>
       </c>
+      <c r="E67" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5.041</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1935,6 +2544,15 @@
       <c r="D68" t="n">
         <v>5.25</v>
       </c>
+      <c r="E68" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.102</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1951,6 +2569,15 @@
       <c r="D69" t="n">
         <v>5.25</v>
       </c>
+      <c r="E69" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="F69" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5.34</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1967,6 +2594,15 @@
       <c r="D70" t="n">
         <v>5.25</v>
       </c>
+      <c r="E70" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5.251</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1983,6 +2619,15 @@
       <c r="D71" t="n">
         <v>5.25</v>
       </c>
+      <c r="E71" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5.087</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1999,6 +2644,15 @@
       <c r="D72" t="n">
         <v>5.05</v>
       </c>
+      <c r="E72" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="F72" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="G72" t="n">
+        <v>5.004</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2015,6 +2669,15 @@
       <c r="D73" t="n">
         <v>4.5</v>
       </c>
+      <c r="E73" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4.391</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2031,6 +2694,15 @@
       <c r="D74" t="n">
         <v>3.2</v>
       </c>
+      <c r="E74" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.995</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2047,6 +2719,15 @@
       <c r="D75" t="n">
         <v>2.1</v>
       </c>
+      <c r="E75" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.094</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2063,6 +2744,15 @@
       <c r="D76" t="n">
         <v>1.95</v>
       </c>
+      <c r="E76" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="F76" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2.013</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2079,6 +2769,15 @@
       <c r="D77" t="n">
         <v>0.5</v>
       </c>
+      <c r="E77" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="F77" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.359</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2095,6 +2794,15 @@
       <c r="D78" t="n">
         <v>0.2</v>
       </c>
+      <c r="E78" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.164</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2111,6 +2819,15 @@
       <c r="D79" t="n">
         <v>0.2</v>
       </c>
+      <c r="E79" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.329</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2127,6 +2844,15 @@
       <c r="D80" t="n">
         <v>0.15</v>
       </c>
+      <c r="E80" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.028</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2143,6 +2869,15 @@
       <c r="D81" t="n">
         <v>0.15</v>
       </c>
+      <c r="E81" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.278</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2159,6 +2894,15 @@
       <c r="D82" t="n">
         <v>0.15</v>
       </c>
+      <c r="E82" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.189</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2175,6 +2919,15 @@
       <c r="D83" t="n">
         <v>0.2</v>
       </c>
+      <c r="E83" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.162</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2191,6 +2944,15 @@
       <c r="D84" t="n">
         <v>0.2</v>
       </c>
+      <c r="E84" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F84" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.026</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2207,6 +2969,15 @@
       <c r="D85" t="n">
         <v>0.2</v>
       </c>
+      <c r="E85" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.348</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2223,6 +2994,15 @@
       <c r="D86" t="n">
         <v>0.15</v>
       </c>
+      <c r="E86" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2239,6 +3019,15 @@
       <c r="D87" t="n">
         <v>0.1</v>
       </c>
+      <c r="E87" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.094</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2255,6 +3044,15 @@
       <c r="D88" t="n">
         <v>0.1</v>
       </c>
+      <c r="E88" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2271,6 +3069,15 @@
       <c r="D89" t="n">
         <v>0.1</v>
       </c>
+      <c r="E89" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F89" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.351</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2287,6 +3094,15 @@
       <c r="D90" t="n">
         <v>0.1</v>
       </c>
+      <c r="E90" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.047</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2303,6 +3119,15 @@
       <c r="D91" t="n">
         <v>0.15</v>
       </c>
+      <c r="E91" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.236</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2319,6 +3144,15 @@
       <c r="D92" t="n">
         <v>0.15</v>
       </c>
+      <c r="E92" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F92" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.161</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2335,6 +3169,15 @@
       <c r="D93" t="n">
         <v>0.15</v>
       </c>
+      <c r="E93" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F93" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.065</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2351,6 +3194,15 @@
       <c r="D94" t="n">
         <v>0.15</v>
       </c>
+      <c r="E94" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="F94" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.092</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2367,6 +3219,15 @@
       <c r="D95" t="n">
         <v>0.1</v>
       </c>
+      <c r="E95" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="F95" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2383,6 +3244,15 @@
       <c r="D96" t="n">
         <v>0.1</v>
       </c>
+      <c r="E96" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="F96" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.083</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2399,6 +3269,15 @@
       <c r="D97" t="n">
         <v>0.1</v>
       </c>
+      <c r="E97" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="F97" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2415,6 +3294,15 @@
       <c r="D98" t="n">
         <v>0.1</v>
       </c>
+      <c r="E98" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.266</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2431,6 +3319,15 @@
       <c r="D99" t="n">
         <v>0.1</v>
       </c>
+      <c r="E99" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F99" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2447,6 +3344,15 @@
       <c r="D100" t="n">
         <v>0.1</v>
       </c>
+      <c r="E100" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.114</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2463,6 +3369,15 @@
       <c r="D101" t="n">
         <v>0.1</v>
       </c>
+      <c r="E101" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="F101" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.289</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2479,6 +3394,15 @@
       <c r="D102" t="n">
         <v>0.1</v>
       </c>
+      <c r="E102" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.205</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2495,6 +3419,15 @@
       <c r="D103" t="n">
         <v>0.1</v>
       </c>
+      <c r="E103" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F103" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.293</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2511,6 +3444,15 @@
       <c r="D104" t="n">
         <v>0.1</v>
       </c>
+      <c r="E104" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2527,6 +3469,15 @@
       <c r="D105" t="n">
         <v>0.2</v>
       </c>
+      <c r="E105" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="F105" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.277</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2543,6 +3494,15 @@
       <c r="D106" t="n">
         <v>0.35</v>
       </c>
+      <c r="E106" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="F106" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.231</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2559,6 +3519,15 @@
       <c r="D107" t="n">
         <v>0.35</v>
       </c>
+      <c r="E107" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2575,6 +3544,15 @@
       <c r="D108" t="n">
         <v>0.35</v>
       </c>
+      <c r="E108" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.274</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2591,6 +3569,15 @@
       <c r="D109" t="n">
         <v>0.45</v>
       </c>
+      <c r="E109" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.471</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2607,6 +3594,15 @@
       <c r="D110" t="n">
         <v>0.7</v>
       </c>
+      <c r="E110" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2623,6 +3619,15 @@
       <c r="D111" t="n">
         <v>0.95</v>
       </c>
+      <c r="E111" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.956</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2639,6 +3644,15 @@
       <c r="D112" t="n">
         <v>1.15</v>
       </c>
+      <c r="E112" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.154</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2655,6 +3669,15 @@
       <c r="D113" t="n">
         <v>1.2</v>
       </c>
+      <c r="E113" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="F113" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.192</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2671,6 +3694,15 @@
       <c r="D114" t="n">
         <v>1.45</v>
       </c>
+      <c r="E114" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="F114" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.619</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2687,6 +3719,15 @@
       <c r="D115" t="n">
         <v>1.75</v>
       </c>
+      <c r="E115" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F115" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.826</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2703,6 +3744,15 @@
       <c r="D116" t="n">
         <v>1.95</v>
       </c>
+      <c r="E116" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="F116" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2.083</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2719,6 +3769,15 @@
       <c r="D117" t="n">
         <v>2.2</v>
       </c>
+      <c r="E117" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="F117" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2.056</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2735,6 +3794,15 @@
       <c r="D118" t="n">
         <v>2.4</v>
       </c>
+      <c r="E118" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="F118" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2.668</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2751,6 +3819,15 @@
       <c r="D119" t="n">
         <v>2.4</v>
       </c>
+      <c r="E119" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="F119" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2.641</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2767,6 +3844,15 @@
       <c r="D120" t="n">
         <v>2.2</v>
       </c>
+      <c r="E120" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="F120" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.238</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2783,6 +3869,15 @@
       <c r="D121" t="n">
         <v>1.65</v>
       </c>
+      <c r="E121" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F121" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1.491</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2799,6 +3894,15 @@
       <c r="D122" t="n">
         <v>1.25</v>
       </c>
+      <c r="E122" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="F122" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.519</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2815,6 +3919,15 @@
       <c r="D123" t="n">
         <v>0.1</v>
       </c>
+      <c r="E123" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2831,6 +3944,15 @@
       <c r="D124" t="n">
         <v>0.1</v>
       </c>
+      <c r="E124" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2847,6 +3969,15 @@
       <c r="D125" t="n">
         <v>0.1</v>
       </c>
+      <c r="E125" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2863,6 +3994,15 @@
       <c r="D126" t="n">
         <v>0.1</v>
       </c>
+      <c r="E126" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.127</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2879,6 +4019,15 @@
       <c r="D127" t="n">
         <v>0.1</v>
       </c>
+      <c r="E127" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2895,6 +4044,15 @@
       <c r="D128" t="n">
         <v>0.1</v>
       </c>
+      <c r="E128" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="F128" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.089</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2911,6 +4069,15 @@
       <c r="D129" t="n">
         <v>0.1</v>
       </c>
+      <c r="E129" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="F129" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.119</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2927,6 +4094,15 @@
       <c r="D130" t="n">
         <v>0.2</v>
       </c>
+      <c r="E130" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="F130" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.266</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2943,6 +4119,15 @@
       <c r="D131" t="n">
         <v>0.95</v>
       </c>
+      <c r="E131" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="F131" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1.142</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2959,6 +4144,15 @@
       <c r="D132" t="n">
         <v>2.3</v>
       </c>
+      <c r="E132" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F132" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.486</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2975,6 +4169,15 @@
       <c r="D133" t="n">
         <v>3.95</v>
       </c>
+      <c r="E133" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="F133" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="G133" t="n">
+        <v>4.263</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2991,6 +4194,15 @@
       <c r="D134" t="n">
         <v>4.65</v>
       </c>
+      <c r="E134" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="F134" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4.643</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3007,6 +4219,15 @@
       <c r="D135" t="n">
         <v>5.1</v>
       </c>
+      <c r="E135" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F135" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="G135" t="n">
+        <v>5.138</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3023,6 +4244,15 @@
       <c r="D136" t="n">
         <v>5.3</v>
       </c>
+      <c r="E136" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="F136" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="G136" t="n">
+        <v>5.151</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3039,6 +4269,15 @@
       <c r="D137" t="n">
         <v>5.35</v>
       </c>
+      <c r="E137" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="F137" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="G137" t="n">
+        <v>5.175</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3055,6 +4294,15 @@
       <c r="D138" t="n">
         <v>5.35</v>
       </c>
+      <c r="E138" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="G138" t="n">
+        <v>5.396</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3071,6 +4319,15 @@
       <c r="D139" t="n">
         <v>5.3</v>
       </c>
+      <c r="E139" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="F139" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4.865</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3087,6 +4344,15 @@
       <c r="D140" t="n">
         <v>5.1</v>
       </c>
+      <c r="E140" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="F140" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="G140" t="n">
+        <v>5.19</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3103,6 +4369,15 @@
       <c r="D141" t="n">
         <v>4.55</v>
       </c>
+      <c r="E141" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="F141" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="G141" t="n">
+        <v>4.499</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3119,6 +4394,15 @@
       <c r="D142" t="n">
         <v>4.35</v>
       </c>
+      <c r="E142" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="F142" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4.217</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3135,6 +4419,15 @@
       <c r="D143" t="n">
         <v>4.35</v>
       </c>
+      <c r="E143" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="F143" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4.435</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3150,6 +4443,15 @@
       </c>
       <c r="D144" t="n">
         <v>4.15</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="F144" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4.155</v>
       </c>
     </row>
   </sheetData>
@@ -18941,7 +20243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18971,6 +20273,16 @@
           <t>Fed Funds Rate (quarterly average)</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Primary Budget Balance (% GDP)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unemployment Rate (%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18987,6 +20299,12 @@
       <c r="D2" t="n">
         <v>3.827</v>
       </c>
+      <c r="E2" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.109999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19003,6 +20321,12 @@
       <c r="D3" t="n">
         <v>3.6</v>
       </c>
+      <c r="E3" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.279999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19019,6 +20343,12 @@
       <c r="D4" t="n">
         <v>3.442</v>
       </c>
+      <c r="E4" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19035,6 +20365,12 @@
       <c r="D5" t="n">
         <v>3.331</v>
       </c>
+      <c r="E5" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19051,6 +20387,12 @@
       <c r="D6" t="n">
         <v>3.254</v>
       </c>
+      <c r="E6" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19067,6 +20409,12 @@
       <c r="D7" t="n">
         <v>3.199</v>
       </c>
+      <c r="E7" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19083,6 +20431,12 @@
       <c r="D8" t="n">
         <v>3.161</v>
       </c>
+      <c r="E8" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19098,6 +20452,12 @@
       </c>
       <c r="D9" t="n">
         <v>3.135</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
